--- a/GILBERT Titouan - Tableau de synthèse - Épreuve E5.xlsx
+++ b/GILBERT Titouan - Tableau de synthèse - Épreuve E5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lajoliverie-my.sharepoint.com/personal/tgilbert_la-joliverie_com/Documents/blog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{8F9BB08C-7C7C-4B6B-9E98-3F439C804877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4AE946-7FD2-405C-9290-9C6290EFA1F4}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{8F9BB08C-7C7C-4B6B-9E98-3F439C804877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19EAB688-FCF2-42F2-A944-11501F3250E1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -155,10 +155,25 @@
     <t>Du 12/01/2026 au 31/03/2026</t>
   </si>
   <si>
-    <t>Projet Java (Ajout de fonctionnalités sur une application Java pour gérer une base de données des salariés d'une entreprise)</t>
-  </si>
-  <si>
     <t>Du 07/04/2026 au 09/04/2026</t>
+  </si>
+  <si>
+    <t>▸Mettre en place et vérifier les niveaux d’habilitation associés à un service
+▸Vérifier les conditions de la continuité d’un service informatique</t>
+  </si>
+  <si>
+    <t>Projet Java InfoWare (Ajout de fonctionnalités sur une application Java pour gérer une base de données des salariés d'une entreprise)</t>
+  </si>
+  <si>
+    <t>▸Analyser les objectifs et les modalités d’organisation d’un projet
+▸Planifier les activités</t>
+  </si>
+  <si>
+    <t>▸Réaliser les tests d’intégration et d’acceptation d’un service
+▸Déployer un service</t>
+  </si>
+  <si>
+    <t>▸Mettre en place son environnement d’apprentissage personnel ▸Développer son projet professionnel</t>
   </si>
 </sst>
 </file>
@@ -504,7 +519,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -580,9 +595,42 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -592,38 +640,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -724,6 +742,10 @@
     </a>
   </bag>
 </FeaturePropertyBags>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1027,56 +1049,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="24"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="25" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="38"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1088,10 +1110,10 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="34" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1114,8 +1136,8 @@
       </c>
     </row>
     <row r="6" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="37"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="19" t="s">
         <v>15</v>
       </c>
@@ -1171,16 +1193,16 @@
       <c r="AQ6"/>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="30"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
@@ -1278,7 +1300,7 @@
       <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="24" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="14" t="s">
@@ -1335,26 +1357,24 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="C10" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>28</v>
-      </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>28</v>
+      <c r="E10" s="14"/>
+      <c r="F10" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>36</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1708,16 +1728,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="33"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2115,16 +2135,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2614,23 +2634,23 @@
     <row r="82" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="45" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="45" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/GILBERT Titouan - Tableau de synthèse - Épreuve E5.xlsx
+++ b/GILBERT Titouan - Tableau de synthèse - Épreuve E5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lajoliverie-my.sharepoint.com/personal/tgilbert_la-joliverie_com/Documents/blog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{8F9BB08C-7C7C-4B6B-9E98-3F439C804877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19EAB688-FCF2-42F2-A944-11501F3250E1}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{8F9BB08C-7C7C-4B6B-9E98-3F439C804877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2C3CCA-447C-4CA0-BA5F-3BD77D4EB862}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>▸Mettre en place son environnement d’apprentissage personnel ▸Développer son projet professionnel</t>
+  </si>
+  <si>
+    <t>Projet Excel (Application de congés</t>
+  </si>
+  <si>
+    <t>Du 26/05/2026 au 19/06/2026</t>
   </si>
 </sst>
 </file>
@@ -598,15 +604,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -630,18 +648,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -742,10 +748,6 @@
     </a>
   </bag>
 </FeaturePropertyBags>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,56 +1051,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="27"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="36" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1110,10 +1112,10 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="38" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1136,8 +1138,8 @@
       </c>
     </row>
     <row r="6" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="35"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="19" t="s">
         <v>15</v>
       </c>
@@ -1193,16 +1195,16 @@
       <c r="AQ6"/>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="30"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
@@ -1362,18 +1364,18 @@
       <c r="B10" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="25" t="s">
         <v>32</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="14"/>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="25" t="s">
         <v>36</v>
       </c>
       <c r="I10"/>
@@ -1414,13 +1416,13 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1728,16 +1730,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1775,14 +1777,28 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="15"/>
+      <c r="A19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
+      <c r="E19" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>28</v>
+      </c>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2135,16 +2151,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="37"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2634,17 +2650,17 @@
     <row r="82" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/GILBERT Titouan - Tableau de synthèse - Épreuve E5.xlsx
+++ b/GILBERT Titouan - Tableau de synthèse - Épreuve E5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lajoliverie-my.sharepoint.com/personal/tgilbert_la-joliverie_com/Documents/blog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{8F9BB08C-7C7C-4B6B-9E98-3F439C804877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2C3CCA-447C-4CA0-BA5F-3BD77D4EB862}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{8F9BB08C-7C7C-4B6B-9E98-3F439C804877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B98FF58A-95BB-4409-8181-F429107899A1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>Du 26/05/2026 au 19/06/2026</t>
+  </si>
+  <si>
+    <t>▸Traiter des demandes concernant les applications</t>
+  </si>
+  <si>
+    <t>▸Développer son projet professionnel</t>
   </si>
 </sst>
 </file>
@@ -189,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -251,6 +257,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -525,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -607,9 +618,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -619,35 +660,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -748,6 +765,10 @@
     </a>
   </bag>
 </FeaturePropertyBags>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1051,56 +1072,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="26"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="27" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="39"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="29"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1112,10 +1133,10 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="35" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1138,8 +1159,8 @@
       </c>
     </row>
     <row r="6" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="39"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="19" t="s">
         <v>15</v>
       </c>
@@ -1195,16 +1216,16 @@
       <c r="AQ6"/>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="34"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
@@ -1730,16 +1751,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1783,21 +1804,19 @@
       <c r="B19" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>28</v>
+      <c r="C19" s="14"/>
+      <c r="D19" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>40</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -2151,16 +2170,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="37"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="34"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2650,17 +2669,17 @@
     <row r="82" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
